--- a/data/trans_orig/IP07C04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28938</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59852</t>
+          <t>60259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74821</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40777</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21027</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>40470</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81479</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>45207</t>
+          <t>43787</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>35277</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>48335</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>70065</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>89699</t>
+          <t>88830</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,36%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>46673</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>65257</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>170150</t>
+          <t>170576</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196528</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>190615</t>
+          <t>190652</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>218211</t>
+          <t>216814</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>370417</t>
+          <t>369016</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>406483</t>
+          <t>407370</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>105345</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>105305</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>166387</t>
+          <t>165532</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>200674</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37687</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36356</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>67283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>81847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>37939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36817</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>52924</t>
+          <t>52438</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69620</t>
+          <t>69334</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>48731</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>33741</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>36757</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>51427</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>95395</t>
+          <t>95212</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39379</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>35219</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>50946</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>70504</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>166874</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>196520</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>184673</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>213243</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>360633</t>
+          <t>360857</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>401399</t>
+          <t>399760</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>102227</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>129177</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>127306</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>209276</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>248068</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37696</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46783</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45991</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87646</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98960</t>
+          <t>99019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14561</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21055</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37328</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51114</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27580</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57453</t>
+          <t>57219</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>30532</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31397</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29206</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>42973</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62305</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>82177</t>
+          <t>81438</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>44148</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>63391</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>40388</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>55172</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>74426</t>
+          <t>74067</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34896</t>
+          <t>35332</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>34648</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>48452</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>73823</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>93274</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>190271</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>220194</t>
+          <t>221744</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>195433</t>
+          <t>195551</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>397743</t>
+          <t>393387</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>438420</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>110181</t>
+          <t>112032</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>141961</t>
+          <t>140237</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>230910</t>
+          <t>229674</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>270385</t>
+          <t>273356</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
